--- a/models/285A_DCF_Model_20260731.xlsx
+++ b/models/285A_DCF_Model_20260731.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A69D5D-4AF4-4D58-B7AD-7983599479F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20D87C8-3472-4AB3-9A31-340615DC9296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,20 @@
     <sheet name="Sensitivity Analysis" sheetId="6" r:id="rId6"/>
     <sheet name="Adjustments Log" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1396,7 +1409,7 @@
       </c>
       <c r="C10" s="5">
         <f>ROUND(AVERAGE(C16:C19),0)</f>
-        <v>19404</v>
+        <v>20929</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="14" x14ac:dyDescent="0.3">
@@ -1414,7 +1427,7 @@
       </c>
       <c r="C12" s="7">
         <f>(C10-C9)/C9</f>
-        <v>-0.51246231155778899</v>
+        <v>-0.47414572864321608</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="14" x14ac:dyDescent="0.3">
@@ -1441,11 +1454,11 @@
       </c>
       <c r="C16" s="11">
         <f>IF('DCF Model'!C53&lt;'DCF Model'!C16,"INVALID (EV &lt; net debt)",'DCF Model'!C55)</f>
-        <v>9121</v>
+        <v>8453</v>
       </c>
       <c r="D16" s="7">
         <f>IF(ISNUMBER(C16),(C16-C9)/C9,"N/A")</f>
-        <v>-0.77082914572864325</v>
+        <v>-0.78761306532663311</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="13.5" x14ac:dyDescent="0.25">
@@ -1454,11 +1467,11 @@
       </c>
       <c r="C17" s="11">
         <f>'DCF Model'!C64</f>
-        <v>9358</v>
+        <v>16126</v>
       </c>
       <c r="D17" s="7">
         <f>(C17-C9)/C9</f>
-        <v>-0.76487437185929652</v>
+        <v>-0.59482412060301504</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="13.5" x14ac:dyDescent="0.25">
@@ -1493,7 +1506,7 @@
       </c>
       <c r="C21" s="6" t="str">
         <f>MIN(C16:C19)&amp;" - "&amp;MAX(C16:C19)</f>
-        <v>9121 - 35031</v>
+        <v>8453 - 35031</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="14" x14ac:dyDescent="0.3">
@@ -1942,7 +1955,7 @@
         <v>62</v>
       </c>
       <c r="C7" s="7">
-        <v>2.3E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -1998,7 +2011,7 @@
         <v>69</v>
       </c>
       <c r="C14" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2065,7 +2078,7 @@
       </c>
       <c r="C23" s="16">
         <f>C7+C8*C9+C10</f>
-        <v>0.11299999999999999</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2092,7 +2105,7 @@
       </c>
       <c r="C26" s="16">
         <f>C23*C24+C11*C25</f>
-        <v>0.10986017955401099</v>
+        <v>0.11661758857032531</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2530,23 +2543,23 @@
       </c>
       <c r="C46" s="21">
         <f>1/(1+C26)^(C19+0)</f>
-        <v>0.9492177814431767</v>
+        <v>0.9463412431447813</v>
       </c>
       <c r="D46" s="21">
         <f>1/(1+C26)^(C19+1)</f>
-        <v>0.85525888659651961</v>
+        <v>0.84750701836645848</v>
       </c>
       <c r="E46" s="21">
         <f>1/(1+C26)^(C19+2)</f>
-        <v>0.77060056965031298</v>
+        <v>0.75899486721463372</v>
       </c>
       <c r="F46" s="21">
         <f>1/(1+C26)^(C19+3)</f>
-        <v>0.6943222072891857</v>
+        <v>0.6797267703676616</v>
       </c>
       <c r="G46" s="21">
         <f>1/(1+C26)^(C19+4)</f>
-        <v>0.62559430465213539</v>
+        <v>0.60873729495695839</v>
       </c>
     </row>
     <row r="47" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2555,23 +2568,23 @@
       </c>
       <c r="C47" s="19">
         <f>C45*C46</f>
-        <v>542767.41760918824</v>
+        <v>541122.59879690234</v>
       </c>
       <c r="D47" s="19">
         <f>D45*D46</f>
-        <v>355740.35389584611</v>
+        <v>352516.0058174649</v>
       </c>
       <c r="E47" s="19">
         <f>E45*E46</f>
-        <v>313455.13160321437</v>
+        <v>308734.31108010677</v>
       </c>
       <c r="F47" s="19">
         <f>F45*F46</f>
-        <v>370731.13422495703</v>
+        <v>362937.94710286957</v>
       </c>
       <c r="G47" s="19">
         <f>G45*G46</f>
-        <v>377080.24349254603</v>
+        <v>366919.59261522052</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2590,7 +2603,7 @@
       </c>
       <c r="C50" s="5">
         <f>SUM(C47:G47)</f>
-        <v>1959774.2808257518</v>
+        <v>1932230.4554125641</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2599,7 +2612,7 @@
       </c>
       <c r="C51" s="5">
         <f>G45*(1+C13)/(C26-C13)</f>
-        <v>6096351.8420704491</v>
+        <v>5709965.8483836893</v>
       </c>
     </row>
     <row r="52" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2608,7 +2621,7 @@
       </c>
       <c r="C52" s="5">
         <f>C51*G46</f>
-        <v>3813842.9915548274</v>
+        <v>3475869.1648417008</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2617,7 +2630,7 @@
       </c>
       <c r="C53" s="5">
         <f>C50+C52</f>
-        <v>5773617.2723805793</v>
+        <v>5408099.6202542651</v>
       </c>
     </row>
     <row r="54" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2626,7 +2639,7 @@
       </c>
       <c r="C54" s="5">
         <f>C53-C16</f>
-        <v>4991135.2723805793</v>
+        <v>4625617.6202542651</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2635,7 +2648,7 @@
       </c>
       <c r="C55" s="24">
         <f>ROUND(C54*1000000/C15,0)</f>
-        <v>9121</v>
+        <v>8453</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2654,7 +2667,7 @@
       </c>
       <c r="C58" s="5">
         <f>C50</f>
-        <v>1959774.2808257518</v>
+        <v>1932230.4554125641</v>
       </c>
     </row>
     <row r="59" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2672,7 +2685,7 @@
       </c>
       <c r="C60" s="5">
         <f>C59*C14</f>
-        <v>6304195.8382312022</v>
+        <v>12608391.676462404</v>
       </c>
     </row>
     <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2681,7 +2694,7 @@
       </c>
       <c r="C61" s="5">
         <f>C60*G46</f>
-        <v>3943869.0118091349</v>
+        <v>7675198.2428875538</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2690,7 +2703,7 @@
       </c>
       <c r="C62" s="5">
         <f>C58+C61</f>
-        <v>5903643.2926348867</v>
+        <v>9607428.6983001176</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2699,7 +2712,7 @@
       </c>
       <c r="C63" s="5">
         <f>C62-C16</f>
-        <v>5121161.2926348867</v>
+        <v>8824946.6983001176</v>
       </c>
     </row>
     <row r="64" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2708,7 +2721,7 @@
       </c>
       <c r="C64" s="24">
         <f>ROUND(C63*1000000/C15,0)</f>
-        <v>9358</v>
+        <v>16126</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -4312,7 +4325,7 @@
       </c>
       <c r="C3" s="16">
         <f>'DCF Model'!C26</f>
-        <v>0.10986017955401099</v>
+        <v>0.11661758857032531</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>180</v>
@@ -4326,7 +4339,7 @@
       </c>
       <c r="I3" s="14">
         <f>'DCF Model'!C14</f>
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
@@ -4370,239 +4383,239 @@
     <row r="7" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B7" s="35">
         <f>$C$3-0.015</f>
-        <v>9.4860179554010993E-2</v>
+        <v>0.10161758857032531</v>
       </c>
       <c r="C7" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B7-C$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10219</v>
+        <v>9422</v>
       </c>
       <c r="D7" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B7-D$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10461</v>
+        <v>9626</v>
       </c>
       <c r="E7" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B7-E$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10716</v>
+        <v>9842</v>
       </c>
       <c r="F7" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B7-F$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10987</v>
+        <v>10070</v>
       </c>
       <c r="G7" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B7-G$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11274</v>
+        <v>10310</v>
       </c>
       <c r="H7" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B7-H$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11579</v>
+        <v>10564</v>
       </c>
       <c r="I7" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B7-I$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11903</v>
+        <v>10834</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B8" s="35">
         <f>$C$3-0.01</f>
-        <v>9.9860179554010997E-2</v>
+        <v>0.10661758857032531</v>
       </c>
       <c r="C8" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B8-C$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9618</v>
+        <v>8898</v>
       </c>
       <c r="D8" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B8-D$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9832</v>
+        <v>9081</v>
       </c>
       <c r="E8" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B8-E$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10057</v>
+        <v>9273</v>
       </c>
       <c r="F8" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B8-F$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10295</v>
+        <v>9474</v>
       </c>
       <c r="G8" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B8-G$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10546</v>
+        <v>9687</v>
       </c>
       <c r="H8" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B8-H$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10813</v>
+        <v>9911</v>
       </c>
       <c r="I8" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B8-I$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11095</v>
+        <v>10147</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B9" s="35">
         <f>$C$3-0.005</f>
-        <v>0.10486017955401099</v>
+        <v>0.1116175885703253</v>
       </c>
       <c r="C9" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B9-C$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9076</v>
+        <v>8424</v>
       </c>
       <c r="D9" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B9-D$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9266</v>
+        <v>8587</v>
       </c>
       <c r="E9" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B9-E$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9466</v>
+        <v>8758</v>
       </c>
       <c r="F9" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B9-F$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9677</v>
+        <v>8938</v>
       </c>
       <c r="G9" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B9-G$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9898</v>
+        <v>9127</v>
       </c>
       <c r="H9" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B9-H$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10132</v>
+        <v>9325</v>
       </c>
       <c r="I9" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B9-I$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10380</v>
+        <v>9535</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B10" s="35">
         <f>$C$3</f>
-        <v>0.10986017955401099</v>
+        <v>0.11661758857032531</v>
       </c>
       <c r="C10" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B10-C$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8586</v>
+        <v>7991</v>
       </c>
       <c r="D10" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B10-D$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8755</v>
+        <v>8138</v>
       </c>
       <c r="E10" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B10-E$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8933</v>
+        <v>8292</v>
       </c>
       <c r="F10" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B10-F$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9121</v>
+        <v>8453</v>
       </c>
       <c r="G10" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B10-G$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9317</v>
+        <v>8621</v>
       </c>
       <c r="H10" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B10-H$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9524</v>
+        <v>8798</v>
       </c>
       <c r="I10" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B10-I$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9742</v>
+        <v>8984</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B11" s="35">
         <f>$C$3+0.005</f>
-        <v>0.114860179554011</v>
+        <v>0.12161758857032531</v>
       </c>
       <c r="C11" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B11-C$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8139</v>
+        <v>7595</v>
       </c>
       <c r="D11" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B11-D$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8291</v>
+        <v>7728</v>
       </c>
       <c r="E11" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B11-E$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8451</v>
+        <v>7866</v>
       </c>
       <c r="F11" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B11-F$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8618</v>
+        <v>8011</v>
       </c>
       <c r="G11" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B11-G$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8793</v>
+        <v>8162</v>
       </c>
       <c r="H11" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B11-H$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8977</v>
+        <v>8321</v>
       </c>
       <c r="I11" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B11-I$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9171</v>
+        <v>8487</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B12" s="35">
         <f>$C$3+0.01</f>
-        <v>0.11986017955401099</v>
+        <v>0.12661758857032532</v>
       </c>
       <c r="C12" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B12-C$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7730</v>
+        <v>7231</v>
       </c>
       <c r="D12" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B12-D$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7868</v>
+        <v>7352</v>
       </c>
       <c r="E12" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B12-E$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8011</v>
+        <v>7477</v>
       </c>
       <c r="F12" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B12-F$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8162</v>
+        <v>7607</v>
       </c>
       <c r="G12" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B12-G$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8319</v>
+        <v>7744</v>
       </c>
       <c r="H12" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B12-H$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8483</v>
+        <v>7886</v>
       </c>
       <c r="I12" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B12-I$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8656</v>
+        <v>8035</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B13" s="35">
         <f>$C$3+0.015</f>
-        <v>0.12486017955401099</v>
+        <v>0.13161758857032529</v>
       </c>
       <c r="C13" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B13-C$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7356</v>
+        <v>6896</v>
       </c>
       <c r="D13" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B13-D$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7480</v>
+        <v>7005</v>
       </c>
       <c r="E13" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B13-E$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7610</v>
+        <v>7119</v>
       </c>
       <c r="F13" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B13-F$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7745</v>
+        <v>7237</v>
       </c>
       <c r="G13" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B13-G$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7887</v>
+        <v>7361</v>
       </c>
       <c r="H13" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B13-H$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8034</v>
+        <v>7489</v>
       </c>
       <c r="I13" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B13-I$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8189</v>
+        <v>7624</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
@@ -4616,269 +4629,269 @@
       </c>
       <c r="C17" s="38">
         <f>$I$3-3</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D17" s="38">
         <f>$I$3-2</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" s="38">
         <f>$I$3-1</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F17" s="38">
         <f>$I$3</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G17" s="38">
         <f>$I$3+1</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H17" s="38">
         <f>$I$3+2</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I17" s="38">
         <f>$I$3+3</f>
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B18" s="35">
         <f>$C$3-0.015</f>
-        <v>9.4860179554010993E-2</v>
+        <v>0.10161758857032531</v>
       </c>
       <c r="C18" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>5333</v>
+        <v>12648</v>
       </c>
       <c r="D18" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>6865</v>
+        <v>14139</v>
       </c>
       <c r="E18" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8397</v>
+        <v>15629</v>
       </c>
       <c r="F18" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9930</v>
+        <v>17120</v>
       </c>
       <c r="G18" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11462</v>
+        <v>18610</v>
       </c>
       <c r="H18" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12995</v>
+        <v>20101</v>
       </c>
       <c r="I18" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>14527</v>
+        <v>21591</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B19" s="35">
         <f>$C$3-0.01</f>
-        <v>9.9860179554010997E-2</v>
+        <v>0.10661758857032531</v>
       </c>
       <c r="C19" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>5231</v>
+        <v>12399</v>
       </c>
       <c r="D19" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>6732</v>
+        <v>13860</v>
       </c>
       <c r="E19" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8233</v>
+        <v>15320</v>
       </c>
       <c r="F19" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9735</v>
+        <v>16781</v>
       </c>
       <c r="G19" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11236</v>
+        <v>18241</v>
       </c>
       <c r="H19" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12737</v>
+        <v>19702</v>
       </c>
       <c r="I19" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>14238</v>
+        <v>21162</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B20" s="35">
         <f>$C$3-0.005</f>
-        <v>0.10486017955401099</v>
+        <v>0.1116175885703253</v>
       </c>
       <c r="C20" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>5131</v>
+        <v>12156</v>
       </c>
       <c r="D20" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>6602</v>
+        <v>13587</v>
       </c>
       <c r="E20" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8073</v>
+        <v>15018</v>
       </c>
       <c r="F20" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9544</v>
+        <v>16449</v>
       </c>
       <c r="G20" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11015</v>
+        <v>17881</v>
       </c>
       <c r="H20" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12486</v>
+        <v>19312</v>
       </c>
       <c r="I20" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>13957</v>
+        <v>20743</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B21" s="35">
         <f>$C$3</f>
-        <v>0.10986017955401099</v>
+        <v>0.11661758857032531</v>
       </c>
       <c r="C21" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>5034</v>
+        <v>11919</v>
       </c>
       <c r="D21" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>6475</v>
+        <v>13321</v>
       </c>
       <c r="E21" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7917</v>
+        <v>14724</v>
       </c>
       <c r="F21" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9358</v>
+        <v>16126</v>
       </c>
       <c r="G21" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10799</v>
+        <v>17529</v>
       </c>
       <c r="H21" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12241</v>
+        <v>18931</v>
       </c>
       <c r="I21" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>13682</v>
+        <v>20334</v>
       </c>
     </row>
     <row r="22" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B22" s="35">
         <f>$C$3+0.005</f>
-        <v>0.114860179554011</v>
+        <v>0.12161758857032531</v>
       </c>
       <c r="C22" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4939</v>
+        <v>11687</v>
       </c>
       <c r="D22" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>6351</v>
+        <v>13061</v>
       </c>
       <c r="E22" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7764</v>
+        <v>14436</v>
       </c>
       <c r="F22" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9176</v>
+        <v>15811</v>
       </c>
       <c r="G22" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10589</v>
+        <v>17185</v>
       </c>
       <c r="H22" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12001</v>
+        <v>18560</v>
       </c>
       <c r="I22" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>13414</v>
+        <v>19934</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B23" s="35">
         <f>$C$3+0.01</f>
-        <v>0.11986017955401099</v>
+        <v>0.12661758857032532</v>
       </c>
       <c r="C23" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4846</v>
+        <v>11460</v>
       </c>
       <c r="D23" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>6230</v>
+        <v>12808</v>
       </c>
       <c r="E23" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7615</v>
+        <v>14155</v>
       </c>
       <c r="F23" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8999</v>
+        <v>15503</v>
       </c>
       <c r="G23" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10383</v>
+        <v>16850</v>
       </c>
       <c r="H23" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11768</v>
+        <v>18197</v>
       </c>
       <c r="I23" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>13152</v>
+        <v>19545</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B24" s="35">
         <f>$C$3+0.015</f>
-        <v>0.12486017955401099</v>
+        <v>0.13161758857032529</v>
       </c>
       <c r="C24" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4755</v>
+        <v>11239</v>
       </c>
       <c r="D24" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>6112</v>
+        <v>12560</v>
       </c>
       <c r="E24" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7469</v>
+        <v>13881</v>
       </c>
       <c r="F24" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8826</v>
+        <v>15202</v>
       </c>
       <c r="G24" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10183</v>
+        <v>16522</v>
       </c>
       <c r="H24" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11539</v>
+        <v>17843</v>
       </c>
       <c r="I24" s="33">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12896</v>
+        <v>19164</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
